--- a/files/temp_files/statement_2025_06.xlsx
+++ b/files/temp_files/statement_2025_06.xlsx
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>194.9</v>
+        <v>-194.9</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -622,7 +622,7 @@
         <v>36</v>
       </c>
       <c r="C4">
-        <v>32.02</v>
+        <v>-32.02</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -636,7 +636,7 @@
         <v>37</v>
       </c>
       <c r="C5">
-        <v>276.76</v>
+        <v>-276.76</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -650,7 +650,7 @@
         <v>38</v>
       </c>
       <c r="C6">
-        <v>46.98</v>
+        <v>-46.98</v>
       </c>
       <c r="D6" t="s">
         <v>60</v>
@@ -664,7 +664,7 @@
         <v>35</v>
       </c>
       <c r="C7">
-        <v>11.09</v>
+        <v>-11.09</v>
       </c>
       <c r="D7" t="s">
         <v>59</v>
@@ -678,7 +678,7 @@
         <v>39</v>
       </c>
       <c r="C8">
-        <v>131.93</v>
+        <v>-131.93</v>
       </c>
       <c r="D8" t="s">
         <v>62</v>
@@ -692,7 +692,7 @@
         <v>38</v>
       </c>
       <c r="C9">
-        <v>47.02</v>
+        <v>-47.02</v>
       </c>
       <c r="D9" t="s">
         <v>60</v>
@@ -706,7 +706,7 @@
         <v>37</v>
       </c>
       <c r="C10">
-        <v>122.65</v>
+        <v>-122.65</v>
       </c>
       <c r="D10" t="s">
         <v>61</v>
@@ -720,7 +720,7 @@
         <v>40</v>
       </c>
       <c r="C11">
-        <v>92.42</v>
+        <v>-92.42</v>
       </c>
       <c r="D11" t="s">
         <v>62</v>
@@ -734,7 +734,7 @@
         <v>41</v>
       </c>
       <c r="C12">
-        <v>159.76</v>
+        <v>-159.76</v>
       </c>
       <c r="D12" t="s">
         <v>59</v>
@@ -748,7 +748,7 @@
         <v>42</v>
       </c>
       <c r="C13">
-        <v>10.52</v>
+        <v>-10.52</v>
       </c>
       <c r="D13" t="s">
         <v>59</v>
@@ -762,7 +762,7 @@
         <v>41</v>
       </c>
       <c r="C14">
-        <v>182.31</v>
+        <v>-182.31</v>
       </c>
       <c r="D14" t="s">
         <v>59</v>
@@ -776,7 +776,7 @@
         <v>43</v>
       </c>
       <c r="C15">
-        <v>6.42</v>
+        <v>-6.42</v>
       </c>
       <c r="D15" t="s">
         <v>60</v>
@@ -790,7 +790,7 @@
         <v>44</v>
       </c>
       <c r="C16">
-        <v>220.95</v>
+        <v>-220.95</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -804,7 +804,7 @@
         <v>43</v>
       </c>
       <c r="C17">
-        <v>5.74</v>
+        <v>-5.74</v>
       </c>
       <c r="D17" t="s">
         <v>60</v>
@@ -818,7 +818,7 @@
         <v>38</v>
       </c>
       <c r="C18">
-        <v>42.33</v>
+        <v>-42.33</v>
       </c>
       <c r="D18" t="s">
         <v>60</v>
@@ -846,7 +846,7 @@
         <v>45</v>
       </c>
       <c r="C20">
-        <v>622.5</v>
+        <v>-622.5</v>
       </c>
       <c r="D20" t="s">
         <v>64</v>
@@ -860,7 +860,7 @@
         <v>44</v>
       </c>
       <c r="C21">
-        <v>157.34</v>
+        <v>-157.34</v>
       </c>
       <c r="D21" t="s">
         <v>63</v>
@@ -888,7 +888,7 @@
         <v>42</v>
       </c>
       <c r="C23">
-        <v>57.29</v>
+        <v>-57.29</v>
       </c>
       <c r="D23" t="s">
         <v>59</v>
@@ -902,7 +902,7 @@
         <v>35</v>
       </c>
       <c r="C24">
-        <v>77.75</v>
+        <v>-77.75</v>
       </c>
       <c r="D24" t="s">
         <v>59</v>
@@ -916,7 +916,7 @@
         <v>42</v>
       </c>
       <c r="C25">
-        <v>50.18</v>
+        <v>-50.18</v>
       </c>
       <c r="D25" t="s">
         <v>59</v>
@@ -930,7 +930,7 @@
         <v>47</v>
       </c>
       <c r="C26">
-        <v>99</v>
+        <v>-99</v>
       </c>
       <c r="D26" t="s">
         <v>65</v>
@@ -944,7 +944,7 @@
         <v>48</v>
       </c>
       <c r="C27">
-        <v>294.58</v>
+        <v>-294.58</v>
       </c>
       <c r="D27" t="s">
         <v>63</v>
@@ -958,7 +958,7 @@
         <v>48</v>
       </c>
       <c r="C28">
-        <v>30.69</v>
+        <v>-30.69</v>
       </c>
       <c r="D28" t="s">
         <v>63</v>
@@ -972,7 +972,7 @@
         <v>41</v>
       </c>
       <c r="C29">
-        <v>44.92</v>
+        <v>-44.92</v>
       </c>
       <c r="D29" t="s">
         <v>59</v>
@@ -986,7 +986,7 @@
         <v>49</v>
       </c>
       <c r="C30">
-        <v>357.09</v>
+        <v>-357.09</v>
       </c>
       <c r="D30" t="s">
         <v>61</v>
@@ -1000,7 +1000,7 @@
         <v>50</v>
       </c>
       <c r="C31">
-        <v>49.36</v>
+        <v>-49.36</v>
       </c>
       <c r="D31" t="s">
         <v>63</v>
@@ -1014,7 +1014,7 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>140.41</v>
+        <v>-140.41</v>
       </c>
       <c r="D32" t="s">
         <v>62</v>
@@ -1028,7 +1028,7 @@
         <v>35</v>
       </c>
       <c r="C33">
-        <v>142.54</v>
+        <v>-142.54</v>
       </c>
       <c r="D33" t="s">
         <v>59</v>
@@ -1042,7 +1042,7 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>48.52</v>
+        <v>-48.52</v>
       </c>
       <c r="D34" t="s">
         <v>62</v>
@@ -1070,7 +1070,7 @@
         <v>47</v>
       </c>
       <c r="C36">
-        <v>69.22</v>
+        <v>-69.22</v>
       </c>
       <c r="D36" t="s">
         <v>65</v>
@@ -1084,7 +1084,7 @@
         <v>51</v>
       </c>
       <c r="C37">
-        <v>29.47</v>
+        <v>-29.47</v>
       </c>
       <c r="D37" t="s">
         <v>62</v>
@@ -1098,7 +1098,7 @@
         <v>52</v>
       </c>
       <c r="C38">
-        <v>72.15000000000001</v>
+        <v>-72.15000000000001</v>
       </c>
       <c r="D38" t="s">
         <v>65</v>
@@ -1112,7 +1112,7 @@
         <v>49</v>
       </c>
       <c r="C39">
-        <v>335.04</v>
+        <v>-335.04</v>
       </c>
       <c r="D39" t="s">
         <v>61</v>
@@ -1126,7 +1126,7 @@
         <v>38</v>
       </c>
       <c r="C40">
-        <v>3.76</v>
+        <v>-3.76</v>
       </c>
       <c r="D40" t="s">
         <v>60</v>
@@ -1154,7 +1154,7 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>46.67</v>
+        <v>-46.67</v>
       </c>
       <c r="D42" t="s">
         <v>65</v>
@@ -1168,7 +1168,7 @@
         <v>39</v>
       </c>
       <c r="C43">
-        <v>85.98</v>
+        <v>-85.98</v>
       </c>
       <c r="D43" t="s">
         <v>62</v>
@@ -1182,7 +1182,7 @@
         <v>36</v>
       </c>
       <c r="C44">
-        <v>11.99</v>
+        <v>-11.99</v>
       </c>
       <c r="D44" t="s">
         <v>60</v>
@@ -1196,7 +1196,7 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>245.27</v>
+        <v>-245.27</v>
       </c>
       <c r="D45" t="s">
         <v>63</v>
@@ -1210,7 +1210,7 @@
         <v>35</v>
       </c>
       <c r="C46">
-        <v>21.05</v>
+        <v>-21.05</v>
       </c>
       <c r="D46" t="s">
         <v>59</v>
@@ -1224,7 +1224,7 @@
         <v>48</v>
       </c>
       <c r="C47">
-        <v>172.92</v>
+        <v>-172.92</v>
       </c>
       <c r="D47" t="s">
         <v>63</v>
@@ -1238,7 +1238,7 @@
         <v>47</v>
       </c>
       <c r="C48">
-        <v>26.32</v>
+        <v>-26.32</v>
       </c>
       <c r="D48" t="s">
         <v>65</v>
@@ -1252,7 +1252,7 @@
         <v>38</v>
       </c>
       <c r="C49">
-        <v>28.24</v>
+        <v>-28.24</v>
       </c>
       <c r="D49" t="s">
         <v>60</v>
@@ -1266,7 +1266,7 @@
         <v>53</v>
       </c>
       <c r="C50">
-        <v>874.77</v>
+        <v>-874.77</v>
       </c>
       <c r="D50" t="s">
         <v>64</v>
@@ -1294,7 +1294,7 @@
         <v>54</v>
       </c>
       <c r="C52">
-        <v>536.6799999999999</v>
+        <v>-536.6799999999999</v>
       </c>
       <c r="D52" t="s">
         <v>64</v>
@@ -1322,7 +1322,7 @@
         <v>47</v>
       </c>
       <c r="C54">
-        <v>77.90000000000001</v>
+        <v>-77.90000000000001</v>
       </c>
       <c r="D54" t="s">
         <v>65</v>
@@ -1336,7 +1336,7 @@
         <v>54</v>
       </c>
       <c r="C55">
-        <v>679.77</v>
+        <v>-679.77</v>
       </c>
       <c r="D55" t="s">
         <v>64</v>
@@ -1350,7 +1350,7 @@
         <v>35</v>
       </c>
       <c r="C56">
-        <v>10.46</v>
+        <v>-10.46</v>
       </c>
       <c r="D56" t="s">
         <v>59</v>
@@ -1378,7 +1378,7 @@
         <v>55</v>
       </c>
       <c r="C58">
-        <v>447.97</v>
+        <v>-447.97</v>
       </c>
       <c r="D58" t="s">
         <v>61</v>
@@ -1392,7 +1392,7 @@
         <v>38</v>
       </c>
       <c r="C59">
-        <v>24.17</v>
+        <v>-24.17</v>
       </c>
       <c r="D59" t="s">
         <v>60</v>
@@ -1420,7 +1420,7 @@
         <v>50</v>
       </c>
       <c r="C61">
-        <v>281.46</v>
+        <v>-281.46</v>
       </c>
       <c r="D61" t="s">
         <v>63</v>
@@ -1434,7 +1434,7 @@
         <v>45</v>
       </c>
       <c r="C62">
-        <v>586.77</v>
+        <v>-586.77</v>
       </c>
       <c r="D62" t="s">
         <v>64</v>
@@ -1448,7 +1448,7 @@
         <v>50</v>
       </c>
       <c r="C63">
-        <v>162.38</v>
+        <v>-162.38</v>
       </c>
       <c r="D63" t="s">
         <v>63</v>
@@ -1476,7 +1476,7 @@
         <v>41</v>
       </c>
       <c r="C65">
-        <v>68.05</v>
+        <v>-68.05</v>
       </c>
       <c r="D65" t="s">
         <v>59</v>
@@ -1490,7 +1490,7 @@
         <v>57</v>
       </c>
       <c r="C66">
-        <v>81.44</v>
+        <v>-81.44</v>
       </c>
       <c r="D66" t="s">
         <v>65</v>
@@ -1504,7 +1504,7 @@
         <v>55</v>
       </c>
       <c r="C67">
-        <v>265.37</v>
+        <v>-265.37</v>
       </c>
       <c r="D67" t="s">
         <v>61</v>
@@ -1532,7 +1532,7 @@
         <v>37</v>
       </c>
       <c r="C69">
-        <v>382.66</v>
+        <v>-382.66</v>
       </c>
       <c r="D69" t="s">
         <v>61</v>
@@ -1546,7 +1546,7 @@
         <v>41</v>
       </c>
       <c r="C70">
-        <v>110.1</v>
+        <v>-110.1</v>
       </c>
       <c r="D70" t="s">
         <v>59</v>
@@ -1574,7 +1574,7 @@
         <v>40</v>
       </c>
       <c r="C72">
-        <v>75.01000000000001</v>
+        <v>-75.01000000000001</v>
       </c>
       <c r="D72" t="s">
         <v>62</v>
@@ -1588,7 +1588,7 @@
         <v>44</v>
       </c>
       <c r="C73">
-        <v>92.26000000000001</v>
+        <v>-92.26000000000001</v>
       </c>
       <c r="D73" t="s">
         <v>63</v>
@@ -1602,7 +1602,7 @@
         <v>49</v>
       </c>
       <c r="C74">
-        <v>43.18</v>
+        <v>-43.18</v>
       </c>
       <c r="D74" t="s">
         <v>61</v>
@@ -1616,7 +1616,7 @@
         <v>54</v>
       </c>
       <c r="C75">
-        <v>279.9</v>
+        <v>-279.9</v>
       </c>
       <c r="D75" t="s">
         <v>64</v>
@@ -1630,7 +1630,7 @@
         <v>54</v>
       </c>
       <c r="C76">
-        <v>92.73999999999999</v>
+        <v>-92.73999999999999</v>
       </c>
       <c r="D76" t="s">
         <v>64</v>
@@ -1644,7 +1644,7 @@
         <v>43</v>
       </c>
       <c r="C77">
-        <v>45.16</v>
+        <v>-45.16</v>
       </c>
       <c r="D77" t="s">
         <v>60</v>
@@ -1658,7 +1658,7 @@
         <v>36</v>
       </c>
       <c r="C78">
-        <v>39.48</v>
+        <v>-39.48</v>
       </c>
       <c r="D78" t="s">
         <v>60</v>
@@ -1686,7 +1686,7 @@
         <v>43</v>
       </c>
       <c r="C80">
-        <v>37.26</v>
+        <v>-37.26</v>
       </c>
       <c r="D80" t="s">
         <v>60</v>
@@ -1700,7 +1700,7 @@
         <v>54</v>
       </c>
       <c r="C81">
-        <v>552.33</v>
+        <v>-552.33</v>
       </c>
       <c r="D81" t="s">
         <v>64</v>
@@ -1728,7 +1728,7 @@
         <v>41</v>
       </c>
       <c r="C83">
-        <v>46.99</v>
+        <v>-46.99</v>
       </c>
       <c r="D83" t="s">
         <v>59</v>
@@ -1756,7 +1756,7 @@
         <v>48</v>
       </c>
       <c r="C85">
-        <v>263.09</v>
+        <v>-263.09</v>
       </c>
       <c r="D85" t="s">
         <v>63</v>
@@ -1770,7 +1770,7 @@
         <v>53</v>
       </c>
       <c r="C86">
-        <v>911.03</v>
+        <v>-911.03</v>
       </c>
       <c r="D86" t="s">
         <v>64</v>
@@ -1784,7 +1784,7 @@
         <v>55</v>
       </c>
       <c r="C87">
-        <v>274.84</v>
+        <v>-274.84</v>
       </c>
       <c r="D87" t="s">
         <v>61</v>
@@ -1798,7 +1798,7 @@
         <v>43</v>
       </c>
       <c r="C88">
-        <v>14.27</v>
+        <v>-14.27</v>
       </c>
       <c r="D88" t="s">
         <v>60</v>
@@ -1812,7 +1812,7 @@
         <v>44</v>
       </c>
       <c r="C89">
-        <v>103.44</v>
+        <v>-103.44</v>
       </c>
       <c r="D89" t="s">
         <v>63</v>
@@ -1826,7 +1826,7 @@
         <v>57</v>
       </c>
       <c r="C90">
-        <v>13.27</v>
+        <v>-13.27</v>
       </c>
       <c r="D90" t="s">
         <v>65</v>
@@ -1840,7 +1840,7 @@
         <v>50</v>
       </c>
       <c r="C91">
-        <v>57.09</v>
+        <v>-57.09</v>
       </c>
       <c r="D91" t="s">
         <v>63</v>
@@ -1854,7 +1854,7 @@
         <v>51</v>
       </c>
       <c r="C92">
-        <v>74.42</v>
+        <v>-74.42</v>
       </c>
       <c r="D92" t="s">
         <v>62</v>
@@ -1868,7 +1868,7 @@
         <v>36</v>
       </c>
       <c r="C93">
-        <v>49.36</v>
+        <v>-49.36</v>
       </c>
       <c r="D93" t="s">
         <v>60</v>
@@ -1882,7 +1882,7 @@
         <v>39</v>
       </c>
       <c r="C94">
-        <v>93.78</v>
+        <v>-93.78</v>
       </c>
       <c r="D94" t="s">
         <v>62</v>
@@ -1896,7 +1896,7 @@
         <v>49</v>
       </c>
       <c r="C95">
-        <v>248.37</v>
+        <v>-248.37</v>
       </c>
       <c r="D95" t="s">
         <v>61</v>
@@ -1910,7 +1910,7 @@
         <v>41</v>
       </c>
       <c r="C96">
-        <v>107.38</v>
+        <v>-107.38</v>
       </c>
       <c r="D96" t="s">
         <v>59</v>
@@ -1952,7 +1952,7 @@
         <v>54</v>
       </c>
       <c r="C99">
-        <v>852.41</v>
+        <v>-852.41</v>
       </c>
       <c r="D99" t="s">
         <v>64</v>
@@ -1966,7 +1966,7 @@
         <v>35</v>
       </c>
       <c r="C100">
-        <v>55.22</v>
+        <v>-55.22</v>
       </c>
       <c r="D100" t="s">
         <v>59</v>
@@ -1980,7 +1980,7 @@
         <v>45</v>
       </c>
       <c r="C101">
-        <v>622</v>
+        <v>-622</v>
       </c>
       <c r="D101" t="s">
         <v>64</v>
@@ -1994,7 +1994,7 @@
         <v>55</v>
       </c>
       <c r="C102">
-        <v>167.25</v>
+        <v>-167.25</v>
       </c>
       <c r="D102" t="s">
         <v>61</v>
@@ -2008,7 +2008,7 @@
         <v>41</v>
       </c>
       <c r="C103">
-        <v>36.71</v>
+        <v>-36.71</v>
       </c>
       <c r="D103" t="s">
         <v>59</v>
@@ -2022,7 +2022,7 @@
         <v>41</v>
       </c>
       <c r="C104">
-        <v>186.08</v>
+        <v>-186.08</v>
       </c>
       <c r="D104" t="s">
         <v>59</v>
@@ -2036,7 +2036,7 @@
         <v>53</v>
       </c>
       <c r="C105">
-        <v>466.8</v>
+        <v>-466.8</v>
       </c>
       <c r="D105" t="s">
         <v>64</v>
@@ -2050,7 +2050,7 @@
         <v>47</v>
       </c>
       <c r="C106">
-        <v>88.44</v>
+        <v>-88.44</v>
       </c>
       <c r="D106" t="s">
         <v>65</v>
@@ -2064,7 +2064,7 @@
         <v>49</v>
       </c>
       <c r="C107">
-        <v>300.23</v>
+        <v>-300.23</v>
       </c>
       <c r="D107" t="s">
         <v>61</v>
@@ -2078,7 +2078,7 @@
         <v>49</v>
       </c>
       <c r="C108">
-        <v>377.77</v>
+        <v>-377.77</v>
       </c>
       <c r="D108" t="s">
         <v>61</v>
@@ -2092,7 +2092,7 @@
         <v>38</v>
       </c>
       <c r="C109">
-        <v>40.91</v>
+        <v>-40.91</v>
       </c>
       <c r="D109" t="s">
         <v>60</v>
@@ -2106,7 +2106,7 @@
         <v>37</v>
       </c>
       <c r="C110">
-        <v>262.27</v>
+        <v>-262.27</v>
       </c>
       <c r="D110" t="s">
         <v>61</v>
@@ -2120,7 +2120,7 @@
         <v>53</v>
       </c>
       <c r="C111">
-        <v>509.63</v>
+        <v>-509.63</v>
       </c>
       <c r="D111" t="s">
         <v>64</v>
@@ -2134,7 +2134,7 @@
         <v>49</v>
       </c>
       <c r="C112">
-        <v>469.64</v>
+        <v>-469.64</v>
       </c>
       <c r="D112" t="s">
         <v>61</v>
@@ -2148,7 +2148,7 @@
         <v>40</v>
       </c>
       <c r="C113">
-        <v>40.72</v>
+        <v>-40.72</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
@@ -2162,7 +2162,7 @@
         <v>49</v>
       </c>
       <c r="C114">
-        <v>322.14</v>
+        <v>-322.14</v>
       </c>
       <c r="D114" t="s">
         <v>61</v>
@@ -2176,7 +2176,7 @@
         <v>42</v>
       </c>
       <c r="C115">
-        <v>101.03</v>
+        <v>-101.03</v>
       </c>
       <c r="D115" t="s">
         <v>59</v>
@@ -2190,7 +2190,7 @@
         <v>44</v>
       </c>
       <c r="C116">
-        <v>148.42</v>
+        <v>-148.42</v>
       </c>
       <c r="D116" t="s">
         <v>63</v>
@@ -2204,7 +2204,7 @@
         <v>40</v>
       </c>
       <c r="C117">
-        <v>104.16</v>
+        <v>-104.16</v>
       </c>
       <c r="D117" t="s">
         <v>62</v>
@@ -2218,7 +2218,7 @@
         <v>54</v>
       </c>
       <c r="C118">
-        <v>956.63</v>
+        <v>-956.63</v>
       </c>
       <c r="D118" t="s">
         <v>64</v>
@@ -2232,7 +2232,7 @@
         <v>55</v>
       </c>
       <c r="C119">
-        <v>334.6</v>
+        <v>-334.6</v>
       </c>
       <c r="D119" t="s">
         <v>61</v>
@@ -2246,7 +2246,7 @@
         <v>49</v>
       </c>
       <c r="C120">
-        <v>56.93</v>
+        <v>-56.93</v>
       </c>
       <c r="D120" t="s">
         <v>61</v>
@@ -2260,7 +2260,7 @@
         <v>38</v>
       </c>
       <c r="C121">
-        <v>23.99</v>
+        <v>-23.99</v>
       </c>
       <c r="D121" t="s">
         <v>60</v>
@@ -2274,7 +2274,7 @@
         <v>36</v>
       </c>
       <c r="C122">
-        <v>34.48</v>
+        <v>-34.48</v>
       </c>
       <c r="D122" t="s">
         <v>60</v>
@@ -2288,7 +2288,7 @@
         <v>37</v>
       </c>
       <c r="C123">
-        <v>470.06</v>
+        <v>-470.06</v>
       </c>
       <c r="D123" t="s">
         <v>61</v>
@@ -2302,7 +2302,7 @@
         <v>44</v>
       </c>
       <c r="C124">
-        <v>299.23</v>
+        <v>-299.23</v>
       </c>
       <c r="D124" t="s">
         <v>63</v>
@@ -2316,7 +2316,7 @@
         <v>44</v>
       </c>
       <c r="C125">
-        <v>279.84</v>
+        <v>-279.84</v>
       </c>
       <c r="D125" t="s">
         <v>63</v>
@@ -2344,7 +2344,7 @@
         <v>57</v>
       </c>
       <c r="C127">
-        <v>84.81</v>
+        <v>-84.81</v>
       </c>
       <c r="D127" t="s">
         <v>65</v>
@@ -2358,7 +2358,7 @@
         <v>39</v>
       </c>
       <c r="C128">
-        <v>110.64</v>
+        <v>-110.64</v>
       </c>
       <c r="D128" t="s">
         <v>62</v>
@@ -2372,7 +2372,7 @@
         <v>53</v>
       </c>
       <c r="C129">
-        <v>513.52</v>
+        <v>-513.52</v>
       </c>
       <c r="D129" t="s">
         <v>64</v>
@@ -2386,7 +2386,7 @@
         <v>54</v>
       </c>
       <c r="C130">
-        <v>236.65</v>
+        <v>-236.65</v>
       </c>
       <c r="D130" t="s">
         <v>64</v>
@@ -2400,7 +2400,7 @@
         <v>57</v>
       </c>
       <c r="C131">
-        <v>49.15</v>
+        <v>-49.15</v>
       </c>
       <c r="D131" t="s">
         <v>65</v>
@@ -2414,7 +2414,7 @@
         <v>40</v>
       </c>
       <c r="C132">
-        <v>78.48999999999999</v>
+        <v>-78.48999999999999</v>
       </c>
       <c r="D132" t="s">
         <v>62</v>
@@ -2428,7 +2428,7 @@
         <v>52</v>
       </c>
       <c r="C133">
-        <v>89.8</v>
+        <v>-89.8</v>
       </c>
       <c r="D133" t="s">
         <v>65</v>
@@ -2442,7 +2442,7 @@
         <v>36</v>
       </c>
       <c r="C134">
-        <v>25.27</v>
+        <v>-25.27</v>
       </c>
       <c r="D134" t="s">
         <v>60</v>
@@ -2470,7 +2470,7 @@
         <v>57</v>
       </c>
       <c r="C136">
-        <v>40.88</v>
+        <v>-40.88</v>
       </c>
       <c r="D136" t="s">
         <v>65</v>
@@ -2484,7 +2484,7 @@
         <v>40</v>
       </c>
       <c r="C137">
-        <v>20.99</v>
+        <v>-20.99</v>
       </c>
       <c r="D137" t="s">
         <v>62</v>
@@ -2498,7 +2498,7 @@
         <v>54</v>
       </c>
       <c r="C138">
-        <v>857.41</v>
+        <v>-857.41</v>
       </c>
       <c r="D138" t="s">
         <v>64</v>
@@ -2526,7 +2526,7 @@
         <v>42</v>
       </c>
       <c r="C140">
-        <v>76.95</v>
+        <v>-76.95</v>
       </c>
       <c r="D140" t="s">
         <v>59</v>
@@ -2540,7 +2540,7 @@
         <v>52</v>
       </c>
       <c r="C141">
-        <v>51.22</v>
+        <v>-51.22</v>
       </c>
       <c r="D141" t="s">
         <v>65</v>
@@ -2554,7 +2554,7 @@
         <v>36</v>
       </c>
       <c r="C142">
-        <v>37.88</v>
+        <v>-37.88</v>
       </c>
       <c r="D142" t="s">
         <v>60</v>
@@ -2568,7 +2568,7 @@
         <v>51</v>
       </c>
       <c r="C143">
-        <v>59.08</v>
+        <v>-59.08</v>
       </c>
       <c r="D143" t="s">
         <v>62</v>
@@ -2582,7 +2582,7 @@
         <v>44</v>
       </c>
       <c r="C144">
-        <v>65.91</v>
+        <v>-65.91</v>
       </c>
       <c r="D144" t="s">
         <v>63</v>
@@ -2596,7 +2596,7 @@
         <v>49</v>
       </c>
       <c r="C145">
-        <v>232.64</v>
+        <v>-232.64</v>
       </c>
       <c r="D145" t="s">
         <v>61</v>
@@ -2610,7 +2610,7 @@
         <v>35</v>
       </c>
       <c r="C146">
-        <v>172.12</v>
+        <v>-172.12</v>
       </c>
       <c r="D146" t="s">
         <v>59</v>
@@ -2624,7 +2624,7 @@
         <v>47</v>
       </c>
       <c r="C147">
-        <v>15.21</v>
+        <v>-15.21</v>
       </c>
       <c r="D147" t="s">
         <v>65</v>
@@ -2638,7 +2638,7 @@
         <v>37</v>
       </c>
       <c r="C148">
-        <v>344.49</v>
+        <v>-344.49</v>
       </c>
       <c r="D148" t="s">
         <v>61</v>
@@ -2666,7 +2666,7 @@
         <v>35</v>
       </c>
       <c r="C150">
-        <v>34.33</v>
+        <v>-34.33</v>
       </c>
       <c r="D150" t="s">
         <v>59</v>
@@ -2708,7 +2708,7 @@
         <v>37</v>
       </c>
       <c r="C153">
-        <v>5.44</v>
+        <v>-5.44</v>
       </c>
       <c r="D153" t="s">
         <v>61</v>
@@ -2722,7 +2722,7 @@
         <v>55</v>
       </c>
       <c r="C154">
-        <v>460.32</v>
+        <v>-460.32</v>
       </c>
       <c r="D154" t="s">
         <v>61</v>
@@ -2736,7 +2736,7 @@
         <v>47</v>
       </c>
       <c r="C155">
-        <v>83.64</v>
+        <v>-83.64</v>
       </c>
       <c r="D155" t="s">
         <v>65</v>
@@ -2778,7 +2778,7 @@
         <v>38</v>
       </c>
       <c r="C158">
-        <v>33.32</v>
+        <v>-33.32</v>
       </c>
       <c r="D158" t="s">
         <v>60</v>
@@ -2792,7 +2792,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>282.31</v>
+        <v>-282.31</v>
       </c>
       <c r="D159" t="s">
         <v>63</v>
@@ -2806,7 +2806,7 @@
         <v>48</v>
       </c>
       <c r="C160">
-        <v>60.9</v>
+        <v>-60.9</v>
       </c>
       <c r="D160" t="s">
         <v>63</v>
@@ -2820,7 +2820,7 @@
         <v>40</v>
       </c>
       <c r="C161">
-        <v>55.45</v>
+        <v>-55.45</v>
       </c>
       <c r="D161" t="s">
         <v>62</v>
@@ -2834,7 +2834,7 @@
         <v>37</v>
       </c>
       <c r="C162">
-        <v>249.77</v>
+        <v>-249.77</v>
       </c>
       <c r="D162" t="s">
         <v>61</v>
@@ -2848,7 +2848,7 @@
         <v>51</v>
       </c>
       <c r="C163">
-        <v>149.84</v>
+        <v>-149.84</v>
       </c>
       <c r="D163" t="s">
         <v>62</v>
@@ -2862,7 +2862,7 @@
         <v>39</v>
       </c>
       <c r="C164">
-        <v>92.68000000000001</v>
+        <v>-92.68000000000001</v>
       </c>
       <c r="D164" t="s">
         <v>62</v>
@@ -2876,7 +2876,7 @@
         <v>41</v>
       </c>
       <c r="C165">
-        <v>175.43</v>
+        <v>-175.43</v>
       </c>
       <c r="D165" t="s">
         <v>59</v>
@@ -2890,7 +2890,7 @@
         <v>53</v>
       </c>
       <c r="C166">
-        <v>18.65</v>
+        <v>-18.65</v>
       </c>
       <c r="D166" t="s">
         <v>64</v>
@@ -2904,7 +2904,7 @@
         <v>55</v>
       </c>
       <c r="C167">
-        <v>376.8</v>
+        <v>-376.8</v>
       </c>
       <c r="D167" t="s">
         <v>61</v>
@@ -2918,7 +2918,7 @@
         <v>49</v>
       </c>
       <c r="C168">
-        <v>445.95</v>
+        <v>-445.95</v>
       </c>
       <c r="D168" t="s">
         <v>61</v>
@@ -2932,7 +2932,7 @@
         <v>36</v>
       </c>
       <c r="C169">
-        <v>4.33</v>
+        <v>-4.33</v>
       </c>
       <c r="D169" t="s">
         <v>60</v>
@@ -2946,7 +2946,7 @@
         <v>41</v>
       </c>
       <c r="C170">
-        <v>40.42</v>
+        <v>-40.42</v>
       </c>
       <c r="D170" t="s">
         <v>59</v>
@@ -2960,7 +2960,7 @@
         <v>43</v>
       </c>
       <c r="C171">
-        <v>39.05</v>
+        <v>-39.05</v>
       </c>
       <c r="D171" t="s">
         <v>60</v>
@@ -2988,7 +2988,7 @@
         <v>45</v>
       </c>
       <c r="C173">
-        <v>646.88</v>
+        <v>-646.88</v>
       </c>
       <c r="D173" t="s">
         <v>64</v>
@@ -3002,7 +3002,7 @@
         <v>45</v>
       </c>
       <c r="C174">
-        <v>207.86</v>
+        <v>-207.86</v>
       </c>
       <c r="D174" t="s">
         <v>64</v>
@@ -3016,7 +3016,7 @@
         <v>37</v>
       </c>
       <c r="C175">
-        <v>402.02</v>
+        <v>-402.02</v>
       </c>
       <c r="D175" t="s">
         <v>61</v>
@@ -3030,7 +3030,7 @@
         <v>54</v>
       </c>
       <c r="C176">
-        <v>44.08</v>
+        <v>-44.08</v>
       </c>
       <c r="D176" t="s">
         <v>64</v>
@@ -3044,7 +3044,7 @@
         <v>52</v>
       </c>
       <c r="C177">
-        <v>11.19</v>
+        <v>-11.19</v>
       </c>
       <c r="D177" t="s">
         <v>65</v>
@@ -3058,7 +3058,7 @@
         <v>49</v>
       </c>
       <c r="C178">
-        <v>460.88</v>
+        <v>-460.88</v>
       </c>
       <c r="D178" t="s">
         <v>61</v>
@@ -3100,7 +3100,7 @@
         <v>38</v>
       </c>
       <c r="C181">
-        <v>12.12</v>
+        <v>-12.12</v>
       </c>
       <c r="D181" t="s">
         <v>60</v>
@@ -3114,7 +3114,7 @@
         <v>53</v>
       </c>
       <c r="C182">
-        <v>793.84</v>
+        <v>-793.84</v>
       </c>
       <c r="D182" t="s">
         <v>64</v>
@@ -3156,7 +3156,7 @@
         <v>52</v>
       </c>
       <c r="C185">
-        <v>19.02</v>
+        <v>-19.02</v>
       </c>
       <c r="D185" t="s">
         <v>65</v>
@@ -3170,7 +3170,7 @@
         <v>53</v>
       </c>
       <c r="C186">
-        <v>556.74</v>
+        <v>-556.74</v>
       </c>
       <c r="D186" t="s">
         <v>64</v>
@@ -3184,7 +3184,7 @@
         <v>40</v>
       </c>
       <c r="C187">
-        <v>29.12</v>
+        <v>-29.12</v>
       </c>
       <c r="D187" t="s">
         <v>62</v>
@@ -3198,7 +3198,7 @@
         <v>51</v>
       </c>
       <c r="C188">
-        <v>67.09</v>
+        <v>-67.09</v>
       </c>
       <c r="D188" t="s">
         <v>62</v>
@@ -3212,7 +3212,7 @@
         <v>45</v>
       </c>
       <c r="C189">
-        <v>41.73</v>
+        <v>-41.73</v>
       </c>
       <c r="D189" t="s">
         <v>64</v>
@@ -3226,7 +3226,7 @@
         <v>36</v>
       </c>
       <c r="C190">
-        <v>37.57</v>
+        <v>-37.57</v>
       </c>
       <c r="D190" t="s">
         <v>60</v>
@@ -3240,7 +3240,7 @@
         <v>52</v>
       </c>
       <c r="C191">
-        <v>97.04000000000001</v>
+        <v>-97.04000000000001</v>
       </c>
       <c r="D191" t="s">
         <v>65</v>
@@ -3268,7 +3268,7 @@
         <v>53</v>
       </c>
       <c r="C193">
-        <v>448.12</v>
+        <v>-448.12</v>
       </c>
       <c r="D193" t="s">
         <v>64</v>
@@ -3296,7 +3296,7 @@
         <v>38</v>
       </c>
       <c r="C195">
-        <v>19.87</v>
+        <v>-19.87</v>
       </c>
       <c r="D195" t="s">
         <v>60</v>
@@ -3310,7 +3310,7 @@
         <v>45</v>
       </c>
       <c r="C196">
-        <v>869.72</v>
+        <v>-869.72</v>
       </c>
       <c r="D196" t="s">
         <v>64</v>
@@ -3324,7 +3324,7 @@
         <v>52</v>
       </c>
       <c r="C197">
-        <v>19.32</v>
+        <v>-19.32</v>
       </c>
       <c r="D197" t="s">
         <v>65</v>
@@ -3338,7 +3338,7 @@
         <v>53</v>
       </c>
       <c r="C198">
-        <v>339.6</v>
+        <v>-339.6</v>
       </c>
       <c r="D198" t="s">
         <v>64</v>
@@ -3352,7 +3352,7 @@
         <v>53</v>
       </c>
       <c r="C199">
-        <v>54.2</v>
+        <v>-54.2</v>
       </c>
       <c r="D199" t="s">
         <v>64</v>
@@ -3380,7 +3380,7 @@
         <v>45</v>
       </c>
       <c r="C201">
-        <v>564.12</v>
+        <v>-564.12</v>
       </c>
       <c r="D201" t="s">
         <v>64</v>
